--- a/fhir/StructureDefinition-ehealth-condition.xlsx
+++ b/fhir/StructureDefinition-ehealth-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,7 +367,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -709,7 +709,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -736,7 +736,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -818,7 +818,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -865,7 +865,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -965,7 +965,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1064,7 +1064,7 @@
     <t>Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1102,7 +1102,7 @@
     <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1148,7 +1148,7 @@
     <t>Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1167,7 +1167,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1208,7 +1208,7 @@
     <t>Condition.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1607,7 +1607,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-condition.xlsx
+++ b/fhir/StructureDefinition-ehealth-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-condition.xlsx
+++ b/fhir/StructureDefinition-ehealth-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-condition.xlsx
+++ b/fhir/StructureDefinition-ehealth-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-condition.xlsx
+++ b/fhir/StructureDefinition-ehealth-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-condition.xlsx
+++ b/fhir/StructureDefinition-ehealth-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-condition.xlsx
+++ b/fhir/StructureDefinition-ehealth-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
